--- a/ValueSet-StatusBildbefundVS.xlsx
+++ b/ValueSet-StatusBildbefundVS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T08:55:06+02:00</t>
+    <t>2025-04-29T14:54:46+02:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-StatusBildbefundVS.xlsx
+++ b/ValueSet-StatusBildbefundVS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T14:54:46+02:00</t>
+    <t>2025-04-29T15:11:56+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -96,7 +96,7 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>nichtVorhanden</t>
+    <t>nicht-vorhanden</t>
   </si>
   <si>
     <t>nicht vorhanden</t>

--- a/ValueSet-StatusBildbefundVS.xlsx
+++ b/ValueSet-StatusBildbefundVS.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T15:11:56+02:00</t>
+    <t>2025-04-29T15:45:38+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
